--- a/artfynd/A 30955-2023 artfynd.xlsx
+++ b/artfynd/A 30955-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130730865</v>
+        <v>129189156</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520930</v>
+        <v>520881</v>
       </c>
       <c r="R2" t="n">
-        <v>6494820</v>
+        <v>6494827</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,6 +799,133 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130730865</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långavik, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>520930</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6494820</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Brunneby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Martin Berry</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Martin Berry</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30955-2023 artfynd.xlsx
+++ b/artfynd/A 30955-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,6 +927,129 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135339851</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57816</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långavik, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520960</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6494776</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunneby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Berry</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Berry</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30955-2023 artfynd.xlsx
+++ b/artfynd/A 30955-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,6 +939,134 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130730865</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135339851</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långavik, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520960</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6494776</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunneby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Berry</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Berry</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339851</t>
         </is>
       </c>
     </row>
@@ -946,6 +1074,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
